--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/63.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/63.xlsx
@@ -426,13 +426,13 @@
         <v>-16.8023716202623</v>
       </c>
       <c r="E2">
-        <v>-16.15776488961372</v>
+        <v>-16.0971784358651</v>
       </c>
       <c r="F2">
-        <v>4.617352062285645</v>
+        <v>1.642996184976074</v>
       </c>
       <c r="G2">
-        <v>-13.35230331625933</v>
+        <v>-14.01436195275161</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.17711354841749</v>
       </c>
       <c r="E3">
-        <v>-14.71026534390594</v>
+        <v>-16.98747189729908</v>
       </c>
       <c r="F3">
-        <v>4.820048595546268</v>
+        <v>2.615353723199801</v>
       </c>
       <c r="G3">
-        <v>-13.10072221563203</v>
+        <v>-13.47905362387912</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.48331612929639</v>
       </c>
       <c r="E4">
-        <v>-16.223463990517</v>
+        <v>-18.87310583172298</v>
       </c>
       <c r="F4">
-        <v>4.604485859785364</v>
+        <v>2.168654944505362</v>
       </c>
       <c r="G4">
-        <v>-12.20341639943536</v>
+        <v>-13.02093275097101</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.78485892107468</v>
       </c>
       <c r="E5">
-        <v>-15.61166715208074</v>
+        <v>-20.0886614672319</v>
       </c>
       <c r="F5">
-        <v>4.188231239878612</v>
+        <v>2.891854478580247</v>
       </c>
       <c r="G5">
-        <v>-11.47792190653434</v>
+        <v>-12.6136215939109</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.08918169128789</v>
       </c>
       <c r="E6">
-        <v>-16.30523917414751</v>
+        <v>-20.01239290799471</v>
       </c>
       <c r="F6">
-        <v>4.456087153043444</v>
+        <v>2.32569020978887</v>
       </c>
       <c r="G6">
-        <v>-11.22923812454402</v>
+        <v>-11.87313519970477</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.42036731512931</v>
       </c>
       <c r="E7">
-        <v>-17.71149337859343</v>
+        <v>-21.02833340924552</v>
       </c>
       <c r="F7">
-        <v>4.590312493523464</v>
+        <v>2.580298871448131</v>
       </c>
       <c r="G7">
-        <v>-11.67182569458972</v>
+        <v>-12.30428771261581</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.77687084664801</v>
       </c>
       <c r="E8">
-        <v>-17.97646344973024</v>
+        <v>-20.48766531204774</v>
       </c>
       <c r="F8">
-        <v>3.671094724189325</v>
+        <v>2.051532077423539</v>
       </c>
       <c r="G8">
-        <v>-10.22026249501477</v>
+        <v>-11.12939055249012</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.18312238738519</v>
       </c>
       <c r="E9">
-        <v>-17.88930843897862</v>
+        <v>-20.04807275470115</v>
       </c>
       <c r="F9">
-        <v>4.285711859105253</v>
+        <v>2.284442483333871</v>
       </c>
       <c r="G9">
-        <v>-9.773061527456491</v>
+        <v>-11.59679071996834</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.64279356423177</v>
       </c>
       <c r="E10">
-        <v>-19.04191828578092</v>
+        <v>-21.57357979366506</v>
       </c>
       <c r="F10">
-        <v>4.336212449449522</v>
+        <v>2.246039370540086</v>
       </c>
       <c r="G10">
-        <v>-9.215598390614632</v>
+        <v>-10.21376239510551</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.15889981065202</v>
       </c>
       <c r="E11">
-        <v>-20.12029285817547</v>
+        <v>-21.7155882100716</v>
       </c>
       <c r="F11">
-        <v>4.311089722857418</v>
+        <v>2.055940648741239</v>
       </c>
       <c r="G11">
-        <v>-8.764561675053361</v>
+        <v>-11.75692745695548</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.73128809937892</v>
       </c>
       <c r="E12">
-        <v>-22.33621557282282</v>
+        <v>-22.18365581197841</v>
       </c>
       <c r="F12">
-        <v>4.291565103173434</v>
+        <v>2.111630132496644</v>
       </c>
       <c r="G12">
-        <v>-7.879258567321141</v>
+        <v>-9.629006057332189</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.35065421138409</v>
       </c>
       <c r="E13">
-        <v>-23.3743954099253</v>
+        <v>-24.61486670942441</v>
       </c>
       <c r="F13">
-        <v>4.249503919928886</v>
+        <v>2.857581605656821</v>
       </c>
       <c r="G13">
-        <v>-7.170455648493013</v>
+        <v>-7.933119819219426</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.03187073463466</v>
       </c>
       <c r="E14">
-        <v>-21.76779245843202</v>
+        <v>-23.57275615688328</v>
       </c>
       <c r="F14">
-        <v>4.515686530940062</v>
+        <v>2.879288145079779</v>
       </c>
       <c r="G14">
-        <v>-6.820152434806695</v>
+        <v>-8.013621308958843</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.778856824874316</v>
       </c>
       <c r="E15">
-        <v>-23.67908019810937</v>
+        <v>-25.63347901033974</v>
       </c>
       <c r="F15">
-        <v>4.387610990058425</v>
+        <v>2.986772129062626</v>
       </c>
       <c r="G15">
-        <v>-6.523205164898507</v>
+        <v>-7.708425048050212</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.593674981237758</v>
       </c>
       <c r="E16">
-        <v>-25.03276787627426</v>
+        <v>-26.54463062305306</v>
       </c>
       <c r="F16">
-        <v>4.663010016793149</v>
+        <v>2.917176013349023</v>
       </c>
       <c r="G16">
-        <v>-5.606556547608913</v>
+        <v>-6.908965258756185</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.476309237213011</v>
       </c>
       <c r="E17">
-        <v>-25.55006451911846</v>
+        <v>-27.84696993444497</v>
       </c>
       <c r="F17">
-        <v>4.535532557176333</v>
+        <v>2.842493721782231</v>
       </c>
       <c r="G17">
-        <v>-4.977598874208312</v>
+        <v>-7.451879459203467</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.414379585457951</v>
       </c>
       <c r="E18">
-        <v>-25.36112299809643</v>
+        <v>-28.85386254462845</v>
       </c>
       <c r="F18">
-        <v>5.057336094812992</v>
+        <v>2.870195984466652</v>
       </c>
       <c r="G18">
-        <v>-4.425448035071193</v>
+        <v>-6.414042204837341</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.412542000398629</v>
       </c>
       <c r="E19">
-        <v>-26.38709859774823</v>
+        <v>-29.76375071309362</v>
       </c>
       <c r="F19">
-        <v>4.777251822048035</v>
+        <v>2.803648260795351</v>
       </c>
       <c r="G19">
-        <v>-4.257200118389106</v>
+        <v>-5.525244596144313</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.466374462393272</v>
       </c>
       <c r="E20">
-        <v>-28.33154382410974</v>
+        <v>-28.70845324424215</v>
       </c>
       <c r="F20">
-        <v>4.961658003054843</v>
+        <v>3.681346599166373</v>
       </c>
       <c r="G20">
-        <v>-4.270964842830977</v>
+        <v>-5.6225853149268</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.568773395962785</v>
       </c>
       <c r="E21">
-        <v>-28.53870792453864</v>
+        <v>-30.43607739935342</v>
       </c>
       <c r="F21">
-        <v>4.799990507254881</v>
+        <v>2.875355056651287</v>
       </c>
       <c r="G21">
-        <v>-3.046029053923753</v>
+        <v>-5.245540145531008</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.712443517404175</v>
       </c>
       <c r="E22">
-        <v>-29.77069965645839</v>
+        <v>-31.04275706216101</v>
       </c>
       <c r="F22">
-        <v>4.927577311368866</v>
+        <v>3.237906617834547</v>
       </c>
       <c r="G22">
-        <v>-2.071926247128282</v>
+        <v>-4.630655631398866</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.881534415540614</v>
       </c>
       <c r="E23">
-        <v>-29.52182151770784</v>
+        <v>-31.63609131206801</v>
       </c>
       <c r="F23">
-        <v>4.487873267023666</v>
+        <v>4.37805494369973</v>
       </c>
       <c r="G23">
-        <v>-1.936625076124579</v>
+        <v>-5.256483019431756</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.07660738965357</v>
       </c>
       <c r="E24">
-        <v>-29.89414585790749</v>
+        <v>-31.11153552538951</v>
       </c>
       <c r="F24">
-        <v>5.008386208246764</v>
+        <v>3.230010619751062</v>
       </c>
       <c r="G24">
-        <v>-1.174771367123348</v>
+        <v>-4.161591884590005</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.29440280529244</v>
       </c>
       <c r="E25">
-        <v>-30.50232218137462</v>
+        <v>-32.60773654481279</v>
       </c>
       <c r="F25">
-        <v>4.825432983664465</v>
+        <v>3.461852431711782</v>
       </c>
       <c r="G25">
-        <v>-1.193946825916743</v>
+        <v>-4.255490601956635</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.52936463896685</v>
       </c>
       <c r="E26">
-        <v>-30.67394228931731</v>
+        <v>-32.93993407683046</v>
       </c>
       <c r="F26">
-        <v>5.203965408782532</v>
+        <v>4.052491643786274</v>
       </c>
       <c r="G26">
-        <v>-1.13741794089063</v>
+        <v>-2.688881212064434</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.77520637073372</v>
       </c>
       <c r="E27">
-        <v>-31.33964155386688</v>
+        <v>-32.60914490022917</v>
       </c>
       <c r="F27">
-        <v>5.084547963994956</v>
+        <v>4.622380252420639</v>
       </c>
       <c r="G27">
-        <v>-0.1431126529536567</v>
+        <v>-3.160776653079095</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.01686225985647</v>
       </c>
       <c r="E28">
-        <v>-31.78343653509258</v>
+        <v>-30.46020058039228</v>
       </c>
       <c r="F28">
-        <v>5.570870869034906</v>
+        <v>4.20920384578269</v>
       </c>
       <c r="G28">
-        <v>0.3012894326144167</v>
+        <v>-3.185169254152007</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.25152014226847</v>
       </c>
       <c r="E29">
-        <v>-30.30216363023559</v>
+        <v>-33.61583599331931</v>
       </c>
       <c r="F29">
-        <v>4.963614606860256</v>
+        <v>3.83206142116652</v>
       </c>
       <c r="G29">
-        <v>-0.5984641748655971</v>
+        <v>-3.520480566533222</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.47410435995638</v>
       </c>
       <c r="E30">
-        <v>-30.16847628481815</v>
+        <v>-32.31536694169257</v>
       </c>
       <c r="F30">
-        <v>5.076257663027739</v>
+        <v>4.050266648942355</v>
       </c>
       <c r="G30">
-        <v>0.2977555569948947</v>
+        <v>-2.96503538095042</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.67630376025353</v>
       </c>
       <c r="E31">
-        <v>-30.56944775159032</v>
+        <v>-30.83470990930062</v>
       </c>
       <c r="F31">
-        <v>5.099067587831225</v>
+        <v>3.753252203198981</v>
       </c>
       <c r="G31">
-        <v>-0.7379160911419975</v>
+        <v>-3.394767124926216</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.84944546405901</v>
       </c>
       <c r="E32">
-        <v>-30.24981220646992</v>
+        <v>-30.50843109281097</v>
       </c>
       <c r="F32">
-        <v>4.74319266791453</v>
+        <v>3.793267318958613</v>
       </c>
       <c r="G32">
-        <v>-0.9374340492855929</v>
+        <v>-2.516482550109649</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.97788983913368</v>
       </c>
       <c r="E33">
-        <v>-30.92398198165083</v>
+        <v>-30.80959725669108</v>
       </c>
       <c r="F33">
-        <v>4.900242843811288</v>
+        <v>3.32727752018778</v>
       </c>
       <c r="G33">
-        <v>-1.802229522271283</v>
+        <v>-1.999352188676484</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.05881021887071</v>
       </c>
       <c r="E34">
-        <v>-29.56147736459301</v>
+        <v>-29.58462013100921</v>
       </c>
       <c r="F34">
-        <v>5.170645158372325</v>
+        <v>3.983965778757088</v>
       </c>
       <c r="G34">
-        <v>-1.162850689197886</v>
+        <v>-3.070949931667736</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.09142514175339</v>
       </c>
       <c r="E35">
-        <v>-29.84808674877547</v>
+        <v>-30.54687783713609</v>
       </c>
       <c r="F35">
-        <v>4.896082782714429</v>
+        <v>3.371384770917242</v>
       </c>
       <c r="G35">
-        <v>-0.9297297410640167</v>
+        <v>-3.014955885755812</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.07475378089023</v>
       </c>
       <c r="E36">
-        <v>-29.38609862322395</v>
+        <v>-30.1522122704196</v>
       </c>
       <c r="F36">
-        <v>5.184845032391114</v>
+        <v>3.8664684896092</v>
       </c>
       <c r="G36">
-        <v>-1.192936209676434</v>
+        <v>-3.387764998118361</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.01108176383059</v>
       </c>
       <c r="E37">
-        <v>-29.21404378177653</v>
+        <v>-29.30254374930843</v>
       </c>
       <c r="F37">
-        <v>4.942300713586224</v>
+        <v>3.599946247962876</v>
       </c>
       <c r="G37">
-        <v>-2.949511921752687</v>
+        <v>-3.366181122700334</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.89866463481027</v>
       </c>
       <c r="E38">
-        <v>-27.31202129991887</v>
+        <v>-28.92906691247383</v>
       </c>
       <c r="F38">
-        <v>5.413592063734975</v>
+        <v>3.698639597067215</v>
       </c>
       <c r="G38">
-        <v>-1.9998443719104</v>
+        <v>-5.248138873006088</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.74833802654017</v>
       </c>
       <c r="E39">
-        <v>-29.2369940880474</v>
+        <v>-28.61642559545828</v>
       </c>
       <c r="F39">
-        <v>5.751836011850486</v>
+        <v>4.016123001333765</v>
       </c>
       <c r="G39">
-        <v>-2.469620143797659</v>
+        <v>-4.891683368895811</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.57259480484054</v>
       </c>
       <c r="E40">
-        <v>-27.33978084558589</v>
+        <v>-28.63597048927538</v>
       </c>
       <c r="F40">
-        <v>5.533557887743205</v>
+        <v>4.493217893506529</v>
       </c>
       <c r="G40">
-        <v>-3.468213988312827</v>
+        <v>-5.585346731448662</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.38042254494507</v>
       </c>
       <c r="E41">
-        <v>-27.34998802599918</v>
+        <v>-27.06742483334257</v>
       </c>
       <c r="F41">
-        <v>5.719849432958786</v>
+        <v>4.623977344773236</v>
       </c>
       <c r="G41">
-        <v>-3.515283111583061</v>
+        <v>-4.635456058540333</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.18064370680603</v>
       </c>
       <c r="E42">
-        <v>-26.0695710572784</v>
+        <v>-26.49590877120453</v>
       </c>
       <c r="F42">
-        <v>5.540173229821963</v>
+        <v>4.448606995396164</v>
       </c>
       <c r="G42">
-        <v>-2.734145663476974</v>
+        <v>-5.186235347065605</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.97515185303551</v>
       </c>
       <c r="E43">
-        <v>-25.14760092016076</v>
+        <v>-23.38739213032731</v>
       </c>
       <c r="F43">
-        <v>5.978495557339293</v>
+        <v>4.463161410663352</v>
       </c>
       <c r="G43">
-        <v>-2.793407806062105</v>
+        <v>-5.810835558235262</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.77440622197584</v>
       </c>
       <c r="E44">
-        <v>-25.62696706471672</v>
+        <v>-24.51482366164696</v>
       </c>
       <c r="F44">
-        <v>5.854898170637189</v>
+        <v>3.855797460726337</v>
       </c>
       <c r="G44">
-        <v>-3.682920721055092</v>
+        <v>-5.146795063921079</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.58914837811817</v>
       </c>
       <c r="E45">
-        <v>-24.55901251101381</v>
+        <v>-26.13856688725927</v>
       </c>
       <c r="F45">
-        <v>6.19401190452564</v>
+        <v>4.531173687902802</v>
       </c>
       <c r="G45">
-        <v>-3.982095940402142</v>
+        <v>-6.565329487278659</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.4238569239609</v>
       </c>
       <c r="E46">
-        <v>-22.74702514937665</v>
+        <v>-24.06183587818569</v>
       </c>
       <c r="F46">
-        <v>6.478600839227021</v>
+        <v>4.296811982302766</v>
       </c>
       <c r="G46">
-        <v>-4.266702536025258</v>
+        <v>-5.431372128550159</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.28079078858742</v>
       </c>
       <c r="E47">
-        <v>-23.12018499303071</v>
+        <v>-24.07781686295876</v>
       </c>
       <c r="F47">
-        <v>6.57942474929136</v>
+        <v>4.424014423941852</v>
       </c>
       <c r="G47">
-        <v>-4.810752039132107</v>
+        <v>-5.61703348804822</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.15445436634541</v>
       </c>
       <c r="E48">
-        <v>-22.67922936500782</v>
+        <v>-24.90526416211429</v>
       </c>
       <c r="F48">
-        <v>6.344494783653004</v>
+        <v>4.631598324878992</v>
       </c>
       <c r="G48">
-        <v>-4.937279223685855</v>
+        <v>-6.436971381094741</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.04552186284667</v>
       </c>
       <c r="E49">
-        <v>-21.83672036130277</v>
+        <v>-22.1618647950535</v>
       </c>
       <c r="F49">
-        <v>6.509308418848799</v>
+        <v>5.048832075055852</v>
       </c>
       <c r="G49">
-        <v>-6.211561303625567</v>
+        <v>-6.899876275036523</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.955971670027269</v>
       </c>
       <c r="E50">
-        <v>-20.44273379294363</v>
+        <v>-21.92804156814145</v>
       </c>
       <c r="F50">
-        <v>7.05863694854568</v>
+        <v>5.121395402806283</v>
       </c>
       <c r="G50">
-        <v>-5.305287908906937</v>
+        <v>-6.892618212947031</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.881442302645272</v>
       </c>
       <c r="E51">
-        <v>-21.14423970147184</v>
+        <v>-20.10405827885798</v>
       </c>
       <c r="F51">
-        <v>6.502229191024474</v>
+        <v>4.582207746854474</v>
       </c>
       <c r="G51">
-        <v>-4.364122004125171</v>
+        <v>-5.642439986583001</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.81716789837542</v>
       </c>
       <c r="E52">
-        <v>-19.15393914730866</v>
+        <v>-22.8769968818708</v>
       </c>
       <c r="F52">
-        <v>6.739236702109052</v>
+        <v>4.752892850201312</v>
       </c>
       <c r="G52">
-        <v>-6.074885300788457</v>
+        <v>-7.055941016068392</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.753533486796419</v>
       </c>
       <c r="E53">
-        <v>-20.25019666355951</v>
+        <v>-18.96458100667792</v>
       </c>
       <c r="F53">
-        <v>6.626066804273389</v>
+        <v>5.309754553059252</v>
       </c>
       <c r="G53">
-        <v>-6.058308569470142</v>
+        <v>-7.033661521679763</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.687563855090572</v>
       </c>
       <c r="E54">
-        <v>-17.25578398225355</v>
+        <v>-19.00511537752058</v>
       </c>
       <c r="F54">
-        <v>6.552517719313626</v>
+        <v>4.34787917595055</v>
       </c>
       <c r="G54">
-        <v>-5.991315868890959</v>
+        <v>-7.477499237139612</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.621135518519738</v>
       </c>
       <c r="E55">
-        <v>-17.05597412361312</v>
+        <v>-16.37288551887409</v>
       </c>
       <c r="F55">
-        <v>7.182111736872169</v>
+        <v>4.652995054893303</v>
       </c>
       <c r="G55">
-        <v>-5.645242149794766</v>
+        <v>-7.628881675006153</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.55183674089427</v>
       </c>
       <c r="E56">
-        <v>-15.95256614690415</v>
+        <v>-18.24416419069368</v>
       </c>
       <c r="F56">
-        <v>6.55623211874778</v>
+        <v>5.213973743743156</v>
       </c>
       <c r="G56">
-        <v>-6.874105560908644</v>
+        <v>-7.922295069294818</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.478116256671525</v>
       </c>
       <c r="E57">
-        <v>-17.66894836529137</v>
+        <v>-17.39819543284677</v>
       </c>
       <c r="F57">
-        <v>7.20691140017718</v>
+        <v>4.755409430371017</v>
       </c>
       <c r="G57">
-        <v>-6.603273533392078</v>
+        <v>-8.599224201894501</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.395387095518382</v>
       </c>
       <c r="E58">
-        <v>-15.63801381385736</v>
+        <v>-16.20076727879056</v>
       </c>
       <c r="F58">
-        <v>6.791233323982777</v>
+        <v>4.596931149071832</v>
       </c>
       <c r="G58">
-        <v>-6.659382422058582</v>
+        <v>-8.487862823388507</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.304406295787768</v>
       </c>
       <c r="E59">
-        <v>-14.92726528987949</v>
+        <v>-17.35716292986327</v>
       </c>
       <c r="F59">
-        <v>6.450913487155851</v>
+        <v>4.417862967608663</v>
       </c>
       <c r="G59">
-        <v>-7.185309738492619</v>
+        <v>-8.236974060510244</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.212536343489099</v>
       </c>
       <c r="E60">
-        <v>-15.11709439180703</v>
+        <v>-17.93736007667401</v>
       </c>
       <c r="F60">
-        <v>6.490466373904721</v>
+        <v>5.233695514869007</v>
       </c>
       <c r="G60">
-        <v>-6.402856520541194</v>
+        <v>-8.660254922900172</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.122359258161987</v>
       </c>
       <c r="E61">
-        <v>-13.85385392499734</v>
+        <v>-14.95872007033677</v>
       </c>
       <c r="F61">
-        <v>6.796493456990554</v>
+        <v>4.11811159596644</v>
       </c>
       <c r="G61">
-        <v>-6.892828211126836</v>
+        <v>-8.201146402302667</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.036343783784664</v>
       </c>
       <c r="E62">
-        <v>-14.13516725882783</v>
+        <v>-15.78464127375172</v>
       </c>
       <c r="F62">
-        <v>6.455665002578309</v>
+        <v>4.828892245938555</v>
       </c>
       <c r="G62">
-        <v>-6.1466062416348</v>
+        <v>-8.780544505269416</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.953332144605978</v>
       </c>
       <c r="E63">
-        <v>-13.62207303986275</v>
+        <v>-14.73531233364236</v>
       </c>
       <c r="F63">
-        <v>6.2884209374227</v>
+        <v>5.003792082630837</v>
       </c>
       <c r="G63">
-        <v>-7.347579269493398</v>
+        <v>-9.978774431904318</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.874198592298832</v>
       </c>
       <c r="E64">
-        <v>-13.65485919167828</v>
+        <v>-14.48478356611601</v>
       </c>
       <c r="F64">
-        <v>6.072462242043257</v>
+        <v>4.573408828301938</v>
       </c>
       <c r="G64">
-        <v>-7.326927260998253</v>
+        <v>-9.799744421177895</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.807147706458506</v>
       </c>
       <c r="E65">
-        <v>-13.00932069341087</v>
+        <v>-13.76231082293229</v>
       </c>
       <c r="F65">
-        <v>6.126753441622736</v>
+        <v>4.476349019715919</v>
       </c>
       <c r="G65">
-        <v>-6.940379673966309</v>
+        <v>-9.547408639591918</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.754378828764711</v>
       </c>
       <c r="E66">
-        <v>-14.39545488784071</v>
+        <v>-14.42860331757686</v>
       </c>
       <c r="F66">
-        <v>6.164541905803644</v>
+        <v>4.467755536279277</v>
       </c>
       <c r="G66">
-        <v>-7.150046450393266</v>
+        <v>-8.570661168219535</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.717755168884334</v>
       </c>
       <c r="E67">
-        <v>-12.59886886630364</v>
+        <v>-12.63635557413914</v>
       </c>
       <c r="F67">
-        <v>5.769473610590893</v>
+        <v>4.195607023233139</v>
       </c>
       <c r="G67">
-        <v>-7.250077770854499</v>
+        <v>-9.011942812084577</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.695730903002122</v>
       </c>
       <c r="E68">
-        <v>-13.10599908500062</v>
+        <v>-14.53467829273253</v>
       </c>
       <c r="F68">
-        <v>5.941624924240687</v>
+        <v>4.782510298321005</v>
       </c>
       <c r="G68">
-        <v>-6.97641404913213</v>
+        <v>-8.709069656040032</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.687109601180522</v>
       </c>
       <c r="E69">
-        <v>-13.9923346601519</v>
+        <v>-14.4339423884319</v>
       </c>
       <c r="F69">
-        <v>5.84585571206823</v>
+        <v>4.029706570004871</v>
       </c>
       <c r="G69">
-        <v>-6.497418044662831</v>
+        <v>-8.402889028663568</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.699675135238301</v>
       </c>
       <c r="E70">
-        <v>-12.61501287614099</v>
+        <v>-13.64437124587652</v>
       </c>
       <c r="F70">
-        <v>5.778673458966384</v>
+        <v>3.992121884205052</v>
       </c>
       <c r="G70">
-        <v>-6.189586962841966</v>
+        <v>-7.20757938921657</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.734548974005314</v>
       </c>
       <c r="E71">
-        <v>-11.64632700116022</v>
+        <v>-12.71478874395199</v>
       </c>
       <c r="F71">
-        <v>5.635440451348322</v>
+        <v>4.081186290619249</v>
       </c>
       <c r="G71">
-        <v>-5.875331249207708</v>
+        <v>-9.4276834273309</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.791970450680619</v>
       </c>
       <c r="E72">
-        <v>-13.16647232689905</v>
+        <v>-14.60835656483732</v>
       </c>
       <c r="F72">
-        <v>5.674628856439961</v>
+        <v>3.631515329683565</v>
       </c>
       <c r="G72">
-        <v>-5.892318133220953</v>
+        <v>-8.03822390821156</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.868056539264133</v>
       </c>
       <c r="E73">
-        <v>-12.5635422405698</v>
+        <v>-15.00960653276096</v>
       </c>
       <c r="F73">
-        <v>5.027557943417155</v>
+        <v>3.734214663547843</v>
       </c>
       <c r="G73">
-        <v>-6.167113876381329</v>
+        <v>-8.210484758860847</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.956709073933704</v>
       </c>
       <c r="E74">
-        <v>-12.62426907701266</v>
+        <v>-13.55621997084321</v>
       </c>
       <c r="F74">
-        <v>5.028661328797685</v>
+        <v>3.807152413364339</v>
       </c>
       <c r="G74">
-        <v>-4.953344084440896</v>
+        <v>-8.272765625280668</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.06220656702804</v>
       </c>
       <c r="E75">
-        <v>-12.06858003153143</v>
+        <v>-12.29399388221124</v>
       </c>
       <c r="F75">
-        <v>5.092152376752655</v>
+        <v>4.476658829124567</v>
       </c>
       <c r="G75">
-        <v>-6.044822748860825</v>
+        <v>-7.277626907067596</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.182052664795924</v>
       </c>
       <c r="E76">
-        <v>-12.06282886954169</v>
+        <v>-14.22737151809801</v>
       </c>
       <c r="F76">
-        <v>5.136286135239007</v>
+        <v>3.293223336258692</v>
       </c>
       <c r="G76">
-        <v>-6.073858278440351</v>
+        <v>-7.031213730396416</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.313660318866328</v>
       </c>
       <c r="E77">
-        <v>-12.11652751432465</v>
+        <v>-13.10282915319525</v>
       </c>
       <c r="F77">
-        <v>4.863827812784222</v>
+        <v>3.694890406202144</v>
       </c>
       <c r="G77">
-        <v>-5.677962491185549</v>
+        <v>-6.627744883782416</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.45176473435451</v>
       </c>
       <c r="E78">
-        <v>-13.58843100645977</v>
+        <v>-13.48007368040423</v>
       </c>
       <c r="F78">
-        <v>4.655751861609819</v>
+        <v>3.519717208266938</v>
       </c>
       <c r="G78">
-        <v>-5.986371068000876</v>
+        <v>-5.878904499485943</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.588067939685216</v>
       </c>
       <c r="E79">
-        <v>-14.39931314769524</v>
+        <v>-14.97599619867603</v>
       </c>
       <c r="F79">
-        <v>4.593629276604274</v>
+        <v>3.40529978912266</v>
       </c>
       <c r="G79">
-        <v>-4.469915149644788</v>
+        <v>-8.160052383492182</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.727503173476562</v>
       </c>
       <c r="E80">
-        <v>-14.72446210991998</v>
+        <v>-15.08875520146703</v>
       </c>
       <c r="F80">
-        <v>4.233161887806458</v>
+        <v>3.418626563898898</v>
       </c>
       <c r="G80">
-        <v>-3.449202590597404</v>
+        <v>-6.240078400198701</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.868218504270336</v>
       </c>
       <c r="E81">
-        <v>-14.93845967762645</v>
+        <v>-14.60913093389263</v>
       </c>
       <c r="F81">
-        <v>4.797700899753543</v>
+        <v>3.086668267635829</v>
       </c>
       <c r="G81">
-        <v>-4.562179818674814</v>
+        <v>-7.350742367076703</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.00901398428282</v>
       </c>
       <c r="E82">
-        <v>-16.62682422732822</v>
+        <v>-16.40938501937592</v>
       </c>
       <c r="F82">
-        <v>4.379042357643868</v>
+        <v>3.050927527674642</v>
       </c>
       <c r="G82">
-        <v>-3.589569967688889</v>
+        <v>-6.269517520030039</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.14720209680681</v>
       </c>
       <c r="E83">
-        <v>-16.23674147630749</v>
+        <v>-16.19863436753295</v>
       </c>
       <c r="F83">
-        <v>4.90297148603611</v>
+        <v>2.802036257829503</v>
       </c>
       <c r="G83">
-        <v>-3.007612511905775</v>
+        <v>-5.601647840155984</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.27594383162475</v>
       </c>
       <c r="E84">
-        <v>-17.48927663056304</v>
+        <v>-17.19614397957253</v>
       </c>
       <c r="F84">
-        <v>4.535121686944544</v>
+        <v>2.936823231408622</v>
       </c>
       <c r="G84">
-        <v>-4.140040821387573</v>
+        <v>-7.685472903241896</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.40417002410785</v>
       </c>
       <c r="E85">
-        <v>-18.04064551184096</v>
+        <v>-19.74655336984844</v>
       </c>
       <c r="F85">
-        <v>4.482490535640275</v>
+        <v>3.186175073529717</v>
       </c>
       <c r="G85">
-        <v>-3.64830383360295</v>
+        <v>-4.288883593767104</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.5336737887863</v>
       </c>
       <c r="E86">
-        <v>-19.56288752104534</v>
+        <v>-18.80566779680075</v>
       </c>
       <c r="F86">
-        <v>4.375548303938859</v>
+        <v>2.60007034461815</v>
       </c>
       <c r="G86">
-        <v>-3.110879116824619</v>
+        <v>-6.486914854451049</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.66658118645421</v>
       </c>
       <c r="E87">
-        <v>-18.86097857833044</v>
+        <v>-21.69854756238073</v>
       </c>
       <c r="F87">
-        <v>4.551127401901437</v>
+        <v>2.645227965214362</v>
       </c>
       <c r="G87">
-        <v>-3.320004491694268</v>
+        <v>-4.304541583048774</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.80363617992685</v>
       </c>
       <c r="E88">
-        <v>-21.17021955685385</v>
+        <v>-21.6776848826274</v>
       </c>
       <c r="F88">
-        <v>3.911632737144635</v>
+        <v>3.178477883622905</v>
       </c>
       <c r="G88">
-        <v>-3.447191201781465</v>
+        <v>-4.952149719793259</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.93851300059785</v>
       </c>
       <c r="E89">
-        <v>-21.83602297630559</v>
+        <v>-22.72443259255238</v>
       </c>
       <c r="F89">
-        <v>4.568045977736213</v>
+        <v>2.94226726197982</v>
       </c>
       <c r="G89">
-        <v>-2.568014134700728</v>
+        <v>-5.557341505438802</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.08360359961278</v>
       </c>
       <c r="E90">
-        <v>-24.78906804755148</v>
+        <v>-26.53197806667563</v>
       </c>
       <c r="F90">
-        <v>3.942398302484609</v>
+        <v>2.433830260754734</v>
       </c>
       <c r="G90">
-        <v>-2.734253943788435</v>
+        <v>-3.702224147489305</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.24202379224587</v>
       </c>
       <c r="E91">
-        <v>-25.37643829719037</v>
+        <v>-26.40710086744011</v>
       </c>
       <c r="F91">
-        <v>3.840762592365526</v>
+        <v>2.487056179854213</v>
       </c>
       <c r="G91">
-        <v>-3.561394118157938</v>
+        <v>-3.602205951914311</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.41700690959625</v>
       </c>
       <c r="E92">
-        <v>-28.13393933231104</v>
+        <v>-27.57287951665671</v>
       </c>
       <c r="F92">
-        <v>3.860153016530257</v>
+        <v>2.513163006920842</v>
       </c>
       <c r="G92">
-        <v>-2.197938279897197</v>
+        <v>-3.463078876572296</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.60859510452238</v>
       </c>
       <c r="E93">
-        <v>-27.77842242339086</v>
+        <v>-28.33554246665852</v>
       </c>
       <c r="F93">
-        <v>3.806721662314883</v>
+        <v>2.033609520296569</v>
       </c>
       <c r="G93">
-        <v>-2.106123138220815</v>
+        <v>-4.977920433921137</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.80769565620992</v>
       </c>
       <c r="E94">
-        <v>-30.45484792411521</v>
+        <v>-31.89724840809036</v>
       </c>
       <c r="F94">
-        <v>3.857808736780334</v>
+        <v>2.015995115843441</v>
       </c>
       <c r="G94">
-        <v>-2.926884617878756</v>
+        <v>-5.163174921945827</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.02537709814394</v>
       </c>
       <c r="E95">
-        <v>-31.85750199172503</v>
+        <v>-33.49812510420093</v>
       </c>
       <c r="F95">
-        <v>3.386432893156498</v>
+        <v>1.497649183746067</v>
       </c>
       <c r="G95">
-        <v>-2.838399916085211</v>
+        <v>-3.690920339217018</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.26381467371937</v>
       </c>
       <c r="E96">
-        <v>-34.96847532975142</v>
+        <v>-35.44517420311686</v>
       </c>
       <c r="F96">
-        <v>3.004900121305491</v>
+        <v>1.112262846737236</v>
       </c>
       <c r="G96">
-        <v>-2.226498032350603</v>
+        <v>-5.913071859584441</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.51958724484607</v>
       </c>
       <c r="E97">
-        <v>-37.06608260400036</v>
+        <v>-35.93471582876804</v>
       </c>
       <c r="F97">
-        <v>2.959258734146043</v>
+        <v>1.357133221209187</v>
       </c>
       <c r="G97">
-        <v>-2.226317565164834</v>
+        <v>-4.824693949538188</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.79421999407285</v>
       </c>
       <c r="E98">
-        <v>-38.6908515289754</v>
+        <v>-41.06334623243795</v>
       </c>
       <c r="F98">
-        <v>2.556569458827537</v>
+        <v>0.8716734750029532</v>
       </c>
       <c r="G98">
-        <v>-3.046672173349405</v>
+        <v>-5.482729808398588</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.06588179544683</v>
       </c>
       <c r="E99">
-        <v>-40.89091326341088</v>
+        <v>-41.54113193956523</v>
       </c>
       <c r="F99">
-        <v>1.988592722158833</v>
+        <v>0.9794573279856137</v>
       </c>
       <c r="G99">
-        <v>-2.333567573056844</v>
+        <v>-2.571446292451907</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.35243108173368</v>
       </c>
       <c r="E100">
-        <v>-44.31109307091801</v>
+        <v>-44.10685210046106</v>
       </c>
       <c r="F100">
-        <v>2.15986927983127</v>
+        <v>0.867286441237727</v>
       </c>
       <c r="G100">
-        <v>-2.810890154530826</v>
+        <v>-5.769259199855538</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.63028981460901</v>
       </c>
       <c r="E101">
-        <v>-46.16051279870256</v>
+        <v>-46.73648035079014</v>
       </c>
       <c r="F101">
-        <v>2.100748698293469</v>
+        <v>0.8321918278507232</v>
       </c>
       <c r="G101">
-        <v>-2.768112869060345</v>
+        <v>-6.985965685091674</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.92533040470503</v>
       </c>
       <c r="E102">
-        <v>-48.34859219091374</v>
+        <v>-48.01128201174141</v>
       </c>
       <c r="F102">
-        <v>1.770732095222563</v>
+        <v>0.02062123087778314</v>
       </c>
       <c r="G102">
-        <v>-3.273148647825398</v>
+        <v>-5.279579537988687</v>
       </c>
     </row>
   </sheetData>
